--- a/fx-server/资源/题库/题目.xlsx
+++ b/fx-server/资源/题库/题目.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -178,17 +178,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -199,18 +199,34 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>这次主题教育的全称是什么？</t>
-        </is>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+          <t>1.（  ）从进攻大城市转到向农村进军，这是中国人民革命发展史上具有决定意义的新起点。</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>武昌起义11</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>南昌起义</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>秋收起义</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>广州起义</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>学习贯彻习近平新时代中国特色社会主义思想主题教育。</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N2" s="2"/>
@@ -219,17 +235,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -240,18 +256,30 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>主题教育“12字”总体要求是什么？</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+          <t>2.我们的党史证明，只要我们不脱离____，和____ 始终保持着紧密的联系，我们就会无往而不胜。.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>群众  人民</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>群众  群众</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>人民  人民</t>
+        </is>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>学思想、强党性、重实践、建新功。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N3" s="2"/>
@@ -260,17 +288,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -281,18 +309,34 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>“四个意识”是什么？</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+          <t>3.在改革开放新时期，邓小平同志成为党的第（  ）代中央领导集体的核心，为开创中国特色社会主义作出了历史性贡献。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>政治意识、大局意识、核心意识、看齐意识。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N4" s="2"/>
@@ -301,17 +345,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -322,18 +366,34 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>“四个自信”是什么？</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+          <t>4.___首次提出并阐述实现中华民族伟大复兴的中国梦？</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2012年</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2013年</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2014年</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2015年</t>
+        </is>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>道路自信、理论自信、制度自信、文化自信。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N5" s="2"/>
@@ -342,17 +402,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -363,18 +423,34 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>国企党建“四个对接”是什么？</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+          <t>5.___是党的新闻舆论工作的根本原则。</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>党的原则</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>党性原则</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>坚持正面舆论原则</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>正面宣传原则</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>体制对接、机制对接、制度对接和工作对接。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N6" s="2"/>
@@ -383,17 +459,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -404,18 +480,34 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>国有经济“五力”是指？</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+          <t>6.一九二七年十月（  ）同志亲自撰写的“牺牲个人，努力革命，阶级斗争，服从组织，严守秘密，永不叛党”人党誓词，句句都是共产党人政治觉悟的生动写照。</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>毛泽东</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>周恩来</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>刘少奇</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>朱  德</t>
+        </is>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>竞争力、创新力、控制力、影响力、抗风险能力。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N7" s="2"/>
@@ -424,17 +516,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -445,18 +537,34 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>确保党永远“三个不变”是哪三个不变？</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+          <t>7.习近平新时代中国特色社会主义思想具有（  ）的鲜明品格，充分体现了当代中国共产党的政治立场、价值追求、精神风范，充盈着高尚真挚的人民情怀、家国情怀、民族情怀、天下情怀，视野极为开阔、气魄极为宏阔、境界极为壮阔。</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>实践性、时代性、创新性</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>实践性、理论性、创新性</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>实践性、时代性、创造性</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>实践性、持久性、创造性</t>
+        </is>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>不变质、不变色、不变味。</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N8" s="2"/>
@@ -465,17 +573,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -486,18 +594,34 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>党的“四自能力”是什么？</t>
-        </is>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+          <t>8.红军长征开始时间____。</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12693</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13058</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13424</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13789</t>
+        </is>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>自我净化、自我完善、自我革新、自我提高能力。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N9" s="2"/>
@@ -506,17 +630,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -527,18 +651,34 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>“四个伟大”是指什么？</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+          <t>9.“建设有中国特色的社会主义”重大命题是在___会议提出的？</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>党的十一届三中全会</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>党的十二大</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>党的十二届三中全会</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>党的十三大</t>
+        </is>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>伟大斗争、伟大工程、伟大事业、伟大梦想。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N10" s="2"/>
@@ -547,17 +687,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第一组</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -568,18 +708,34 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>“四大考验”是什么？</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+          <t>10.党中央在延安（  ）年，形成了伟大的延安精神。</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>十</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>十一</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>十二</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>十三</t>
+        </is>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>执政考验、改革开放考验、市场经济考验、外部环境考验。</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="2"/>
@@ -588,17 +744,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -609,18 +765,34 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>“四种危险”是什么？</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+          <t>11.在共产党与民主党派的关系上，毛泽东倡导的方针是（  ）。</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>加强团结，共同发展</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>长期共存，互相监督</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>和平共处，同舟共济</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>肝胆相照，荣辱与共</t>
+        </is>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>精神懈怠危险、能力不足危险、脱离群众危险、消极腐败危险。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N12" s="2"/>
@@ -629,17 +801,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -650,18 +822,34 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>新时代党的建设的根本原则是什么？</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+          <t>12.遵义会议纠正了在第____次反“围剿”斗争中所犯的“左”倾机会主义性质的原则错误。</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>坚持和加强党的全面领导。</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N13" s="2"/>
@@ -670,17 +858,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -691,18 +879,34 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>新时代党的建设的根本方针是什么？</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+          <t>13.长征途中翻越的第一座人迹罕至的大雪山是——（  ）。</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>昆仑山</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>大别山</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>狼牙山</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>夹金山</t>
+        </is>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>坚持党要管党，全面从严治党。</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="2"/>
@@ -711,17 +915,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -732,18 +936,34 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>新时代党的建设的主线是什么？</t>
-        </is>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+          <t>14.标志着中国新民主主义革命开端的历史事件是（  ）。</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>新文化运动</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>五四运动</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>中国共产党成立</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>五卅运动</t>
+        </is>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>加强党的长期执政能力建设、先进性和纯洁性建设。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N15" s="2"/>
@@ -752,17 +972,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -773,18 +993,34 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>检验主题教育的根本评判标准是什么？</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+          <t>15.第一次国共合作正式建立的标志是（  ）。</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>国民党第一次全国代表大会的召开</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>中共三大的召开</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>黄埔军校的建立</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>北伐战争的开始</t>
+        </is>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>群众满意不满意。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N16" s="2"/>
@@ -793,17 +1029,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -814,18 +1050,34 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>主题教育的范围是什么？</t>
-        </is>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+          <t>16.1949年3月，党的七届二中全会在河北____召开，毛泽东同志提出“两个务必”重要思想。在这里，党中央和毛泽东同志指挥了三大战役，指导革命取得全国胜利，进而建立了新中国。</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>瓦窑堡</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>井冈山</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>红旗渠</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>西柏坡</t>
+        </is>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>以县处级以上领导干部为重点，在全党开展。</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N17" s="2"/>
@@ -834,17 +1086,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -855,18 +1107,34 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>五大新发展理念是什么？</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+          <t>17.党员干部首先要把学习贯彻（  ）作为理论武装的重中之重，在学懂弄通做实上下苦功夫，以党的创新理论滋养初心、引领使命。</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>习近平新时代中国特色社会主义思想</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>马克思主义</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>毛泽东思想</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>邓小平理论</t>
+        </is>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>创新、协调、绿色、开放、共享。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N18" s="2"/>
@@ -875,17 +1143,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -896,18 +1164,34 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>“三新一高”战略部署是指什么？</t>
-        </is>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+          <t>18.(多选)“两个维护”是保证全党团结统一、步调一致，带领全国各族人民决胜全面建成小康社会、奋力夺取新时代中国特色社会主义伟大胜利的根本政治保证。下面属于“两个维护”内容的是（  ）。</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>坚决维护习近平总书记党中央的核心、全党的核心地位</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>坚决维护宪法的根本大法地位，全面依法治国</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>坚决维护中国特色社会主义理论体系，坚持理论自信</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>坚决维护党中央权威和集中统一领导</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>立足新发展阶段、贯彻新发展理念、构建新发展格局，推动高质量发展。</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="N19" s="2"/>
@@ -916,17 +1200,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -937,18 +1221,34 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>“三去一降一补”是指什么？</t>
-        </is>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+          <t>19.党的二十大报告指出，我们坚持走中国特色社会主义政治发展道路，全面发展全过程人民民主，社会主义民主政治制度化、规范化、程序化全面推进，人民当家作主更为扎实，（  ）总体格局基本形成。</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>全面从严治党</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>全面依法治国</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>全面深化改革</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>全面建设社会主义现代化国家</t>
+        </is>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>去产能、去库存、去杠杆、降成本、补短板。</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N20" s="2"/>
@@ -957,17 +1257,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>第二组</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -978,18 +1278,34 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>习近平总书记调查研究“五字诀”是什么？</t>
-        </is>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+          <t>20.(单选)党的二十大报告指出，面对影响党长期执政、国家长治久安、人民幸福安康的突出矛盾和问题，党中央审时度势、果敢抉择，锐意进取、攻坚克难，团结带领全党全军全国各族人民撸起袖子加油干、风雨无阻向前行，义无反顾进行具有许多新的历史特点的（  ）。</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>伟大斗争</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>伟大工程</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>伟大事业</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>伟大梦想</t>
+        </is>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>深、实、细、准、效。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N21" s="2"/>
@@ -998,17 +1314,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>必答题</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>简单题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1019,18 +1335,34 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>“三重一大”事项具体是指什么？</t>
-        </is>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+          <t>21.(单选)党的二十大报告指出，（  ）为新时代党和国家事业发展提供了根本遵循。</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>用新时代中国特色社会主义思想武装头脑、指导实践、推动工作</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>全面加强党的领导</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>以中国式现代化推进中华民族伟大复兴</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>着力推进高质量发展</t>
+        </is>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>重大决策、重要人事任免、重大项目安排、大额资金使用。</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N22" s="2"/>
@@ -1049,7 +1381,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1060,30 +1392,34 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>下列选项中，哪些不属于“四不两直”中“四不”的内容（  ）</t>
+          <t>22.(单选)党的二十大报告指出，我们对新时代党和国家事业发展作出科学完整的战略部署，明确“（  ）”总体布局和“（  ）”战略布局。</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>不发通知</t>
+          <t>两个维护 四个现代化</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>不穿制服</t>
+          <t>四个现代化 两个维护</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>不打招呼</t>
-        </is>
-      </c>
-      <c r="J23" s="2"/>
+          <t>四个全面 五位一体</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>五位一体 四个全面</t>
+        </is>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N23" s="2"/>
@@ -1102,7 +1438,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1113,30 +1449,34 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>下列内容不属于“五位一体”总体布局的是（  ）</t>
+          <t>23.(单选)党的二十大报告指出，我们贯彻总体国家安全观，国家安全领导体制和法治体系、战略体系、政策体系不断完善，在（  ）上寸步不让，以坚定的意志品质维护国家主权、安全、发展利益，国家安全得到全面加强。</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>经济建设</t>
+          <t>领土问题</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>政治建设</t>
+          <t>原则问题</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>民主法治建设</t>
-        </is>
-      </c>
-      <c r="J24" s="2"/>
+          <t>主权问题</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>内政问题</t>
+        </is>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N24" s="2"/>
@@ -1155,7 +1495,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1166,30 +1506,34 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>全党必须牢记“两个永远在路上”：（  ），党的自我革命永远在路上。</t>
+          <t>24.(单选)党的二十大报告指出，我们确立党在新时代的强军目标，坚决把全军工作重心归正到（  ）上来，中国特色强军之路越走越宽广。</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>思想建设永远在路上</t>
+          <t>备战打仗</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>严格管党永远在路上</t>
+          <t>提升战斗力</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>全面从严治党永远在路上</t>
-        </is>
-      </c>
-      <c r="J25" s="2"/>
+          <t>军事训练</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>军队改革</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N25" s="2"/>
@@ -1208,7 +1552,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1219,25 +1563,29 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>党在新时代的强军目标是建设一支听党指挥、（  ）、作风优良的人民军队，把人民军队建设成为世界一流军队。</t>
+          <t>25.(单选)党的二十大报告指出，我们深入推进全面从严治党，坚持打铁必须自身硬，从制定和落实（  ）开局破题，提出和落实新时代党的建设总要求。</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>战无不胜</t>
+          <t>监督执纪“四种形态”</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>纪律严明</t>
+          <t>中国共产党纪律检查委员会工作条例</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>能打胜仗</t>
-        </is>
-      </c>
-      <c r="J26" s="2"/>
+          <t>中央八项规定</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>三严三实主题教育</t>
+        </is>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="inlineStr">
@@ -1261,7 +1609,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1272,30 +1620,34 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>中国革命的“三大法宝”是什么（  ）</t>
+          <t>26.(单选)党的二十大报告指出，拥有（  ）理论指导是我们党坚定信仰信念、把握历史主动的根本所在。</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>统一战线、武装斗争、党的建设</t>
+          <t>辩证唯物主义</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>实事求是、群众路线、独立自主</t>
+          <t>马克思主义科学</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>政治路线、组织路线、思想路线</t>
-        </is>
-      </c>
-      <c r="J27" s="2"/>
+          <t>历史唯物主义</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>科学社会主义</t>
+        </is>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N27" s="2"/>
@@ -1314,7 +1666,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1325,30 +1677,34 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>党中央决定从今年4月开始，在全党自上而下分（ ）开展学习贯彻习近平新时代中国特色社会主义思想主题教育。</t>
+          <t>27.(单选)党的二十大报告指出，十八大以来，我们党勇于进行理论探索和创新，以全新的视野深化对共产党执政规律、社会主义建设规律、人类社会发展规律的认识，取得重大理论创新成果，集中体现为（  ）。</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>一批</t>
+          <t>中国特色社会主义思想</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>两批</t>
+          <t>马克思主义中国化理论</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>三批</t>
-        </is>
-      </c>
-      <c r="J28" s="2"/>
+          <t>新时代中国特色社会主义思想</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>中国特色新发展思想</t>
+        </is>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N28" s="2"/>
@@ -1367,7 +1723,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1378,30 +1734,34 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会，是在全党全国各族人民迈（   ）、向第二个百年奋斗目标进军的关键时刻召开的一次十分重要的大会。</t>
+          <t>29.(单选)“六个必须坚持”是新时代中国特色社会主义思想的世界观和方法论。“六个必须坚持”不包括（  ）。</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全面建设社会主义现代化国家新征程</t>
+          <t>坚持自信自立</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>全面建设中国特色社会主义现代化国家新征程</t>
+          <t>坚持系统观念</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>建设中国特色社会主义现代化国家新征程</t>
-        </is>
-      </c>
-      <c r="J29" s="2"/>
+          <t>坚持守正创新</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>坚持中国共产党领导</t>
+        </is>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N29" s="2"/>
@@ -1420,7 +1780,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1431,30 +1791,34 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>习近平总书记强调指出，（ ）是谋事之基、成事之道。</t>
+          <t>30.党的全国代表大会（  ）年举办一次。</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>调查研究</t>
+          <t>三</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>理论学习</t>
+          <t>五</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>建章立制</t>
-        </is>
-      </c>
-      <c r="J30" s="2"/>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>八</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N30" s="2"/>
@@ -1473,7 +1837,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1484,30 +1848,34 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>党中央决定，在全党大兴（ ），作为在全党开展的主题教育的重要内容，推动全面建设社会主义现代化国家开好局起好步。</t>
+          <t>31、必须更好发挥法治固根本、稳预期、利长远的保障作用，在法治轨道上（  ）。</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>理论学习</t>
+          <t>全面建设社会主义现代化强国</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>调查研究</t>
+          <t>全面建设社会主义国家</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>作风整顿</t>
-        </is>
-      </c>
-      <c r="J31" s="2"/>
+          <t>建设社会主义现代化强国</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>建设社会主义现代化国家</t>
+        </is>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N31" s="2"/>
@@ -1526,7 +1894,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>选择题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1537,34 +1905,4541 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>开展主题教育，要教育引导广大党员、干部学思想、见行动，树立正确的（ ），政绩观、事业观，增强责任感和使命感。</t>
+          <t>32、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们创立了新时代中国特色社会主义思想，明确坚持和发展中国特色社会主义的基本方略，提出一系列治国理政（  ）。</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>权力观</t>
+          <t>新理念新思想新道路</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>道德观</t>
+          <t>中国智慧中国方案中国力量</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>价值观</t>
-        </is>
-      </c>
-      <c r="J32" s="2"/>
+          <t>中国效率中国方案中国力量</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>新理念新思想新战略</t>
+        </is>
+      </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>33、要加强人民当家作主制度保障，坚持和完善我国根本政治制度、基本政治制度、重要政治制度，拓展民主渠道，丰富民主形式，支持和保证人民通过（  ）行使国家权力。</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>人民代表大会</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>投票</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>选举</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>网络监督</t>
+        </is>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>34、习近平指出，从党的十八大开始，中国特色社会主义进入（  ）。</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>新征程</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>新阶段</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>新时代</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>新局面</t>
+        </is>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>35、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们坚持绿水青山就是金山银山的理念，坚持（  ）一体化保护和系统治理。</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>山水林湖草沙</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>山水林田湖草</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>山水田湖草沙</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>山水林田湖草沙</t>
+        </is>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>36、我们实行更加积极主动的开放战略，构建面向全球的高标准自由贸易区网络，加快推进自由贸易试验区、（  ）自由贸易港建设，共建“一带一路”成为深受欢迎的国际公共产品和国际合作平台。</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>37、新时代十年的伟大变革，在党史、新中国史、改革开放史、社会主义发展史、中华民族发展史上具有（  ）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>划时代意义</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>跨时代意义</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>里程碑意义</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>丰碑意义</t>
+        </is>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>38、五年来，我们坚持加强党的全面领导和（  ）集中统一领导，全力推进全面建成小康社会进程。</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>各级政府</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>党中央</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>地方政府</t>
+        </is>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>39、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，推进以（  ）为主体的自然保护地体系建设。</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>天然林</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>国家公园</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>生物多样性</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>湿地</t>
+        </is>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>40、坚持多劳多得，鼓励勤劳致富，促进（  ），增加低收入者收入，扩大中等收入群体。</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>机会公平</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>机会平等</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>机遇公平</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>机遇平等</t>
+        </is>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>抢答题</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>41、全方位夯实粮食安全根基，牢牢守住（  ）亩耕地红线。</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>十七亿</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>十八亿</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>十九亿</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>二十亿</t>
+        </is>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>42、面对国际局势急剧变化，我们保持战略定力，发扬斗争精神，在斗争中维护国家尊严和核心利益，牢牢掌握了我国（  ）。</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>发展和社会安全</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>发展和安全主动权</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>发展和社会稳定</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>发展和领土安全</t>
+        </is>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>43、我们经过接续奋斗，实现了（  ）这个中华民族的千年梦想。</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>中国梦</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>小康</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>强国</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>强军</t>
+        </is>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>44、党的二十大开幕的时间是（  ）。</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2022年10月16日</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2022年10月17日</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2022年10月15日</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2022年10月18日</t>
+        </is>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>45、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们坚持（  ）的理念。</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>保卫母亲河</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>节能减排创造价值</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>天朗气清好生活</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>绿水青山就是金山银山</t>
+        </is>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>46、深化国企国资改革。落实国有科技型企业（  ）政策。</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>薪资调整</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>股权激励</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>股权和分红激励</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>分红激励</t>
+        </is>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>47、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，拥有（  ）是我们党坚定信仰信念、把握历史主动的根本所在。</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>科学社会主义</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>坚持人民主体地位</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>马克思主义科学理论指导</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>不断推进自我革命</t>
+        </is>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>48、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，加快建设世界重要人才中心和创新高地，着力形成人才国际竞争的（  ）优势。</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全面</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>比较</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>绝对</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>最强</t>
+        </is>
+      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>49、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，治国有常，（  ）为本。</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>利民</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>农民</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>领导</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>大众</t>
+        </is>
+      </c>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>50、（  ）是国家安全的根本。</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>经济安全</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>政治安全</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>生态安全</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>生物安全</t>
+        </is>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>51、加大财政资源统筹力度，积极盘活各类资金资产，稳妥化解（  ）。</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>金融危机</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>债务风险</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>存量隐性债务</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>地方债务</t>
+        </is>
+      </c>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>52、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们要办好人民满意的教育，全面贯彻党的教育方针，落实立德树人根本任务，培养（  ）的社会主义建设者和接班人。</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>又红又专</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>四有新人</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>德智体美劳全面发展</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>德才兼备</t>
+        </is>
+      </c>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>53、推进（  ）建设，推动工业固体废物和再生资源规模化、高值化利用。</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>生态产品交易中心</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>生态保护补偿机制</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>工业资源综合利用基地</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>森林质量精准提升工程</t>
+        </is>
+      </c>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>54、全党同志务必不忘初心、牢记使命，务必谦虚谨慎、艰苦奋斗，务必（  ），坚定历史自信，增强历史主动，谱写新时代中国特色社会主义更加绚丽的华章。</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>勇于斗争、善于斗争</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>敢于斗争、乐于斗争</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>敢于斗争、善于斗争</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>勇于斗争、乐于斗争</t>
+        </is>
+      </c>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>55、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，加强同（  ）的团结合作。</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>广大群众</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>非政界人士</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>国内外人士</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>民主党派和无党派人士</t>
+        </is>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>20分</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>56、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，必须牢固树立和践行（  ）的理念。</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>绿水青山就是金山银山</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>只要绿水青山不要金山银山</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>金山银山就是绿水青山</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>既要绿水青山又要金山银山</t>
+        </is>
+      </c>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>57、中国坚定奉行（  ）的和平外交政策。</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>互帮互助</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>不结盟</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>独立自主</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>互不干涉</t>
+        </is>
+      </c>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>58、坚持（  ）在我国现代化建设全局中的核心地位。</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>人才</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>创新</t>
+        </is>
+      </c>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>59、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，十年来，我们对新时代党和国家事业发展作出科学完整的战略部署，确定（  ）工作总基调。</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>稳中求进</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>稳中求快</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>进中求快</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>进中求稳</t>
+        </is>
+      </c>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>60、习近平总书记在党的二十大报告提出“三个务必”是指（  ）。</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>务必不忘初心、牢记使命，务必谦虚谨慎、艰苦奋斗，务必敢于斗争、善于斗争</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>务必保持清醒头脑、务必发扬艰苦作风、务必迎接风险挑战</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>务必放下架子接地气、务必扑下身子转作风、务必扎下根子办实事</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>以上答案都不对</t>
+        </is>
+      </c>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>61、我国的分配制度是（  ）。</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>按劳分配为主体、按需分配为辅</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>按需分配为主体、按劳分配为辅</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>按劳分配为主体、多种分配方式并存</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>按需分配为主体、多种分配方式并存</t>
+        </is>
+      </c>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>62、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）原则，把新时代好干部标准落到实处。</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>党管人才</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>以德为先</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>党管干部</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>德才兼备</t>
+        </is>
+      </c>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>63、全党必须牢记，全面从严治党永远在路上，（  ）永远在路上。</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>党的自我革命</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>党的自我革新</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>党的自我完善</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>党的自我提高</t>
+        </is>
+      </c>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>64、全面依法治国是（  ）的一场深刻革命，关系党执政兴国，关系人民幸福安康，关系党和国家长治久安。</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>国家治理</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>顶层设计</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>治理能力</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>法治社会</t>
+        </is>
+      </c>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>65、不断谱写马克思主义中国化时代化新篇章，是当代中国共产党人的庄严（  ）。</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>政治责任</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>重要任务</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>重点工作</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>历史责任</t>
+        </is>
+      </c>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>66、健全资本市场功能，提高（  ）融资比重。</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>间接</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>直接</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>67、全心全意依靠（  ），健全以职工代表大会为基本形式的企事业单位民主管理制度，维护职工合法权益。</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>群体组织</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>基层党组织</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>群团组织</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>工人阶级</t>
+        </is>
+      </c>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>68、发展壮大医疗卫生队伍，把工作重点放在（  ）。</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>乡村和社区</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>农村和居委会</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>农村和社区</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>农村和小区</t>
+        </is>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>69、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化是（  ）的现代化。</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全面建成小康社会</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>社会主义的现代化</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>实现中华民族伟大复兴</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>全体人民共同富裕</t>
+        </is>
+      </c>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>70、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化的本质要求是：实现（  ）发展。</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>高水平</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>高效</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>高质量</t>
+        </is>
+      </c>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>71、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化的本质要求是：推动构建人类命运共同体，创造（  ）。</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>人类文明新业态</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>人类文明新形态</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>人精神文明新形态</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>政治文明新形态</t>
+        </is>
+      </c>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>72、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，建设（  ）的高素质干部队伍。</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>德才兼备</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>通才与专才相结合</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>革命化、年轻化、知识化、专业化</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>堪当民族复兴重任</t>
+        </is>
+      </c>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>73、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）对外开放。</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全方位</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>全天候</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>全面</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>高水平</t>
+        </is>
+      </c>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>74、（  ）是社会主义的生命，是全面建设社会主义现代化国家的应有之义。</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>人民代表大会</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>社会民主</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>国家富强</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>人民民主</t>
+        </is>
+      </c>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>75、十九大以来的五年，是（  ）的五年。</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>极不寻常、极不平凡</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>党和国家发展进程中极不平凡</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>我们经受住各种困难和风险考验、夺取全面建设小康社会新胜利</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>不平凡</t>
+        </is>
+      </c>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>76、没有坚实的（  ）基础，就不可能全面建成社会主义现代化强国。</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>政治文化</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>经济产业</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>物质技术</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>自然资源</t>
+        </is>
+      </c>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>77、要坚持党的领导、人民当家作主、依法治国（  ）。</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>辩证统一</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>有机统一</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>相互协调</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>协调统一</t>
+        </is>
+      </c>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>78、治国有常，利民为本。（  ）是立党为公、执政为民的本质要求。</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>为民请命</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>为民谋福</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>为民造福</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>为民解难</t>
+        </is>
+      </c>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>79、全党必须牢记，坚持（  ）是坚持和发展中国特色社会主义的必由之路。</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>群众路线</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>人民民主</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>以人民为中心</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>党的全面领导</t>
+        </is>
+      </c>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>80、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，（  ）是实现中华民族伟大复兴的必由之路。</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>团结奋斗</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>中国特色社会主义</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>新发展理念</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>全面从严治党</t>
+        </is>
+      </c>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>81、习近平总书记在党的二十大报告中指出：“（  ）是立党为公、执政为民的本质要求。”</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>为民造福</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>为民服务</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>为民着想</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>为民干事</t>
+        </is>
+      </c>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>82、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）是坚持和发展中国特色社会主义的必由之路。</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>党的全面领导</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>全面从严治党</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>以人民为中心</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>新发展理念</t>
+        </is>
+      </c>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>83、（  ）大，（  ）全会提出的“十个明确”、“十四个坚持”、“十三个方面成就”概括了这一思想的主要内容，必须长期坚持并不断丰富发展。</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>十九 十九届六中</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>十九 十九届五中</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>十八 十八届六中</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>十八 十八届五中</t>
+        </is>
+      </c>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>84、全面依法治国的重点任务和主体工程是（  ）。</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>法治国家</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>法治政府</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>法治社会</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>法治公民</t>
+        </is>
+      </c>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>85、到（  ）年，我国农村基本具备现代生活条件。</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>二O二五年</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>二O五O年</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>二O三O年</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>二O三五年</t>
+        </is>
+      </c>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>86、习近平总书记代表第十九届中央委员会向大会作的报告共分（  ）部分。</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>十四</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>十五</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>十六</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>十七</t>
+        </is>
+      </c>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>87、为民造福是立党为公、执政为民的（  ）。</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>根本要求</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>基本要求</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>首要要求</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>本质要求</t>
+        </is>
+      </c>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>88、维护社会公平正义的最后一道防线是（  ）。</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>公正司法</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>严格执法</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>科学立法</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>全民守法</t>
+        </is>
+      </c>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>89、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国坚持（  ），推动建设一个清洁美丽的世界。</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>循环发展</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>创新发展</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>绿色低碳</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>简约适度</t>
+        </is>
+      </c>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>90、发展是党执政兴国的第一（  ）。</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>要务</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>使命</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>责任</t>
+        </is>
+      </c>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>91、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，江山就是人民，人民就是江山。中国共产党领导人民打江山、守江山，守的是（  ）。</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>国泰民安</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>人民的心</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>公平自由</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>人民民主</t>
+        </is>
+      </c>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>92、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们贯彻（  ）。</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>国家安全观</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>总体安全观</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>国家安全总体观</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>总体国家安全观</t>
+        </is>
+      </c>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>93、健全（  ）的社会治理制度，提升社会治理效能。</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>共建共治共用</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>共建共治共享</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>共聚共治共享</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>共建共治共有</t>
+        </is>
+      </c>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>94、深入推进全面（  ），坚持打铁必须自身硬，提出和落实新时代党的建设总要求。</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>依法治党</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>依法治国</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>从严治党</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>从严治国</t>
+        </is>
+      </c>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>95、（  ）是我们立党立国、兴党兴国的根本指导思想。</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>马克思主义</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>毛泽东思想</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>邓小平理论</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>“三个代表”重要思想</t>
+        </is>
+      </c>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>96、（  ）是历史的创造者。</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>群众</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>公民</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>党员</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>人民群众</t>
+        </is>
+      </c>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>97、全党必须牢记，全面（  ）永远在路上，党的（  ）永远在路上。</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>依法治党 自我革命</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>依法治党 自我革新</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>从严治党 自我革命</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>从严治党 自我革新</t>
+        </is>
+      </c>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>98、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，深入开展社会主义核心价值观宣传教育，深化爱国主义、集体主义、社会主义教育，着力培养（  ）。</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>实现中国特色社会主义共同理想的新人</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>实现共产主义远大理想的时代新人</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>担当民族复兴大任的时代新人</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>有担当、有理想、有本领的时代新人</t>
+        </is>
+      </c>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>99、习近平总书记在党的二十大报告中指出，党用伟大奋斗创造了百年伟业，也一定能用（  ）创造新的伟业。</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>奋斗</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>伟大奋斗</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>新的伟大奋斗</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>团结奋斗</t>
+        </is>
+      </c>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>100、习近平总书记在党的二十大报告中指出，走过百年奋斗历程的中国共产党在革命性锻造中更加坚强有力，党的政治领导力、思想引领力、群众组织力、社会号召力显著增强，党同人民群众始终保持血肉联系，中国共产党在世界形势深刻变化的历史进程中始终走在（  ），在应对国内外各种风险和考验的历史进程中始终成为全国人民的主心骨，在坚持和发展中国特色社会主义的历史进程中始终成为坚强领导核心。</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>时代前列</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>时代前沿</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>历史前列</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>历史前沿</t>
+        </is>
+      </c>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1、必须坚持在发展中保障和改善民生，鼓励（  ）创造美好生活，不断实现人民对美好生活的向往。</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>团结奋斗</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>共同努力</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>共同奋斗</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>踔厉奋进</t>
+        </is>
+      </c>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2、以铸牢中华民族共同体意识为主线，加强和改进党的（  ）。</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>民族工作</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>民族团结工作</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>宗教工作</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>综治工作</t>
+        </is>
+      </c>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>3、加强和改进侨务工作，形成共同致力民族复兴的（  ）。</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>核心力量</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>重要力量</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>强大力量</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>关键力量</t>
+        </is>
+      </c>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>4、党的二十大报告中指出，（  ）是党执政兴国的第一要务。</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>法治</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>安全</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>发展</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>稳定</t>
+        </is>
+      </c>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>5、（  ）是实现中华民族伟大复兴的必由之路。</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>坚持党的全面领导</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>中国特色社会主义</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>团结奋斗</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>全面从严治党</t>
+        </is>
+      </c>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>6、构筑法治国家的基础是（  ）。</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>法治国家</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>法治政府</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>法治社会</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>法治公民</t>
+        </is>
+      </c>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>7、必须增强忧患意识，坚持（  ），做到居安思危、未雨绸缪，准备经受风高浪急甚至惊涛骇浪的重大考验。</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>底线思维</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>辩证思维</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>创新思维</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>法治思维</t>
+        </is>
+      </c>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>8、坚持和完善“（  ）”是新时代党解决台湾问题总体方略的根本保证。</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>和平发展</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>一国两制</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>民族区域自治</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>九二共识</t>
+        </is>
+      </c>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>9、党的二十大报告中指出，实施（  ），推进各类资源节约集约利用，加快构建废弃物循环利用体系。</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>全面节约战略</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>深度节约战略</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>节约优先战略</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>资源循环利用战略</t>
+        </is>
+      </c>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>10、我国基本实现社会主义现代化的时间节点是（  ）。</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2020-2035年</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2022-2035年</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>2025-2035年</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2016-2022年</t>
+        </is>
+      </c>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>共答题</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>11、发展壮大医疗卫生队伍，把工作重点放在（  ）。</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>城市和街道</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>城市和农村</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>农村和街道</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>农村和社区</t>
+        </is>
+      </c>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fx-server/资源/题库/题目.xlsx
+++ b/fx-server/资源/题库/题目.xlsx
@@ -183,12 +183,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -240,7 +240,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -293,7 +293,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -350,7 +350,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>第一组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -783,11 +783,7 @@
           <t>和平共处，同舟共济</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>肝胆相照，荣辱与共</t>
-        </is>
-      </c>
+      <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="inlineStr">
@@ -801,12 +797,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -858,12 +854,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>长风破浪</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -915,12 +911,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -972,12 +968,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1029,12 +1025,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1086,12 +1082,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1143,12 +1139,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1200,12 +1196,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1257,12 +1253,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>第二组</t>
+          <t>一路长虹</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1314,12 +1310,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1371,12 +1367,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1428,12 +1424,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1485,12 +1481,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1542,12 +1538,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1599,12 +1595,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1656,12 +1652,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1713,12 +1709,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1770,12 +1766,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1827,12 +1823,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1884,12 +1880,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1941,12 +1937,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1998,12 +1994,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,12 +2051,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2112,12 +2108,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2226,12 +2222,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2283,12 +2279,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2340,12 +2336,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2397,12 +2393,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>抢答题</t>
+          <t>咫尺天涯</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2454,12 +2450,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2511,12 +2507,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2568,12 +2564,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2625,12 +2621,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2682,12 +2678,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2739,12 +2735,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2796,12 +2792,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2853,12 +2849,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2910,12 +2906,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2967,12 +2963,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3024,12 +3020,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3081,12 +3077,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3138,12 +3134,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3195,12 +3191,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3252,12 +3248,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>20分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3309,12 +3305,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3366,12 +3362,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3423,12 +3419,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>抢答题</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3480,12 +3476,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3524,8 +3520,16 @@
           <t>以上答案都不对</t>
         </is>
       </c>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -3537,12 +3541,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3594,12 +3598,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3651,12 +3655,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3708,12 +3712,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3765,12 +3769,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3822,12 +3826,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3879,12 +3883,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3936,12 +3940,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>30分</t>
+          <t>10分</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3993,12 +3997,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4050,12 +4054,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4107,12 +4111,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4164,12 +4168,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4221,12 +4225,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4278,12 +4282,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4335,12 +4339,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4392,12 +4396,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4449,12 +4453,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>20分</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4506,12 +4510,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4563,12 +4567,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4620,12 +4624,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4677,12 +4681,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4734,12 +4738,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4791,12 +4795,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4848,12 +4852,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4905,12 +4909,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4962,12 +4966,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5019,12 +5023,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5076,12 +5080,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5133,12 +5137,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5190,12 +5194,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>共答题</t>
+          <t>30分</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">

--- a/fx-server/资源/题库/题目.xlsx
+++ b/fx-server/资源/题库/题目.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -178,14 +178,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -193,40 +189,48 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E2" s="2"/>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>小游戏.mp4</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1.（  ）从进攻大城市转到向农村进军，这是中国人民革命发展史上具有决定意义的新起点。</t>
+          <t>慢性肾脏病患者合并肾性贫血时，其红细胞形态通常表现为？( )</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>武昌起义11</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>南昌起义</t>
+          <t>球形红细胞</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>秋收起义</t>
+          <t>椭圆形红细胞</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>广州起义</t>
-        </is>
-      </c>
-      <c r="K2" s="2"/>
+          <t>靶形红细胞</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>正常形态红细胞</t>
+        </is>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N2" s="2"/>
@@ -235,14 +239,10 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -250,36 +250,48 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
+          <t>音频</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>时间到.wav</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2.我们的党史证明，只要我们不脱离____，和____ 始终保持着紧密的联系，我们就会无往而不胜。.</t>
+          <t>哪项不是肾性贫血的临床表现？( )</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>群众  人民</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>群众  群众</t>
+          <t>面色苍白</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>人民  人民</t>
-        </is>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+          <t>乏力</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>心悸</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>黄疸</t>
+        </is>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="2"/>
@@ -288,14 +300,10 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -303,40 +311,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>文字</t>
+          <t>图片</t>
         </is>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3.在改革开放新时期，邓小平同志成为党的第（  ）代中央领导集体的核心，为开创中国特色社会主义作出了历史性贡献。</t>
+          <t>q11.png</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>控制蛋白质摄入</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>增加磷的摄入</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
+          <t>维持营养平衡</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>减少钠盐摄入</t>
+        </is>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>q11.png</t>
         </is>
       </c>
       <c r="N4" s="2"/>
@@ -345,14 +357,10 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -366,34 +374,38 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4.___首次提出并阐述实现中华民族伟大复兴的中国梦？</t>
+          <t>慢性肾功能不全患者出现贫血时，应首先考虑哪种可能性？( )</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2012年</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2013年</t>
+          <t>缺铁性贫血</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2014年</t>
+          <t>溶血性贫血</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2015年</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
+          <t>肾性贫血</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>再生障碍性贫血</t>
+        </is>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N5" s="2"/>
@@ -402,14 +414,10 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -423,34 +431,38 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5.___是党的新闻舆论工作的根本原则。</t>
+          <t>关于慢性肾脏病的透析治疗，以下哪些说法正确？()</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>党的原则</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>党性原则</t>
+          <t>透析可清除血液中的废物和多余液体</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>坚持正面舆论原则</t>
+          <t>透析分为血液透析和腹膜透析</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>正面宣传原则</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
+          <t>腹膜透析中，透析液通过细管吸收废物和多余液体</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>透析可以完全治愈慢性肾脏病</t>
+        </is>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N6" s="2"/>
@@ -459,14 +471,10 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -480,34 +488,38 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6.一九二七年十月（  ）同志亲自撰写的“牺牲个人，努力革命，阶级斗争，服从组织，严守秘密，永不叛党”人党誓词，句句都是共产党人政治觉悟的生动写照。</t>
+          <t>慢性肾脏病治疗中，如何纠正酸碱平衡失调？( )</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>毛泽东</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>周恩来</t>
+          <t>使用碱性药物</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>刘少奇</t>
+          <t>限制酸性饮食</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>朱  德</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
+          <t>纠正电解质紊乱</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>增加酸性药物摄入</t>
+        </is>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N7" s="2"/>
@@ -516,14 +528,10 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -537,34 +545,30 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7.习近平新时代中国特色社会主义思想具有（  ）的鲜明品格，充分体现了当代中国共产党的政治立场、价值追求、精神风范，充盈着高尚真挚的人民情怀、家国情怀、民族情怀、天下情怀，视野极为开阔、气魄极为宏阔、境界极为壮阔。</t>
+          <t>肾病综合征病人最突出的体征是什么？( )</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>实践性、时代性、创新性</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>实践性、理论性、创新性</t>
+          <t>高血压</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>实践性、时代性、创造性</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>实践性、持久性、创造性</t>
-        </is>
-      </c>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N8" s="2"/>
@@ -573,14 +577,10 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -594,34 +594,38 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8.红军长征开始时间____。</t>
+          <t>慢性肾脏病的治疗中，如何控制感染？( )</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>使用广谱抗生素</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>根据病原体选择抗生素</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
-        </is>
-      </c>
-      <c r="K9" s="2"/>
+          <t>长期使用抗生素预防感染</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>提高患者免疫力</t>
+        </is>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B,D</t>
         </is>
       </c>
       <c r="N9" s="2"/>
@@ -630,14 +634,10 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -651,34 +651,42 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9.“建设有中国特色的社会主义”重大命题是在___会议提出的？</t>
+          <t>肾病综合征病人易自发形成血栓的主要原因是？( )</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>党的十一届三中全会</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>党的十二大</t>
+          <t>血管内皮易受损伤</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>党的十二届三中全会</t>
+          <t>红细胞增多</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>党的十三大</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+          <t>组织因子释放</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>高脂血症</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>血小板增多</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N10" s="2"/>
@@ -687,14 +695,10 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -708,34 +712,38 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10.党中央在延安（  ）年，形成了伟大的延安精神。</t>
+          <t>肾病综合征病人24小时尿蛋白定量常为多少？( )</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>十</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>十一</t>
+          <t>2.5g/d</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>十二</t>
+          <t>3.5g/d</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>十三</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
+          <t>150mg/d</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1.5g/d</t>
+        </is>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N11" s="2"/>
@@ -744,14 +752,10 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -765,30 +769,38 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11.在共产党与民主党派的关系上，毛泽东倡导的方针是（  ）。</t>
+          <t>肾病综合征严重水肿病人起身应慢，以防止什么？( )</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>加强团结，共同发展</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>长期共存，互相监督</t>
+          <t>体位性低血压</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>和平共处，同舟共济</t>
-        </is>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>坠床</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>皮肤损伤</t>
+        </is>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N12" s="2"/>
@@ -797,14 +809,10 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -818,34 +826,30 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12.遵义会议纠正了在第____次反“围剿”斗争中所犯的“左”倾机会主义性质的原则错误。</t>
+          <t>能确定肾病综合征的病理类型的检查项目是什么？( )</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>中段尿培养</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>六</t>
-        </is>
-      </c>
+          <t>尿蛋白定量</t>
+        </is>
+      </c>
+      <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N13" s="2"/>
@@ -854,14 +858,10 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>长风破浪</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -875,34 +875,38 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13.长征途中翻越的第一座人迹罕至的大雪山是——（  ）。</t>
+          <t>关于慢性肾脏病的饮食疗法，以下哪些说法正确？( )</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>昆仑山</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>大别山</t>
+          <t>应限制蛋白质摄入</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>狼牙山</t>
+          <t>应增加磷的摄入</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>夹金山</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
+          <t>应控制钠盐摄入</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>应限制钾的摄入</t>
+        </is>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N14" s="2"/>
@@ -911,14 +915,10 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -932,34 +932,38 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14.标志着中国新民主主义革命开端的历史事件是（  ）。</t>
+          <t>糖尿病肾病最早期的临床表现是？( )</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>新文化运动</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>五四运动</t>
+          <t>大量白蛋白尿</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>中国共产党成立</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>五卅运动</t>
-        </is>
-      </c>
-      <c r="K15" s="2"/>
+          <t>微量白蛋白尿</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>脓尿</t>
+        </is>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N15" s="2"/>
@@ -968,14 +972,10 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -989,34 +989,38 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15.第一次国共合作正式建立的标志是（  ）。</t>
+          <t>糖尿病肾病的英文及缩写为？( )</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>国民党第一次全国代表大会的召开</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>中共三大的召开</t>
+          <t>Nephrotic Syndrome(NS)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>黄埔军校的建立</t>
+          <t>Diabetic Kidney Disease(DKD)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>北伐战争的开始</t>
-        </is>
-      </c>
-      <c r="K16" s="2"/>
+          <t>Systemic Lupus Erythematosus(SLE)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease(CKD)</t>
+        </is>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N16" s="2"/>
@@ -1025,14 +1029,10 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1046,34 +1046,38 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16.1949年3月，党的七届二中全会在河北____召开，毛泽东同志提出“两个务必”重要思想。在这里，党中央和毛泽东同志指挥了三大战役，指导革命取得全国胜利，进而建立了新中国。</t>
+          <t>慢性肾脏病患者使用利尿剂时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>瓦窑堡</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>井冈山</t>
+          <t>监测电解质平衡</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>红旗渠</t>
+          <t>长期使用利尿剂</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>西柏坡</t>
-        </is>
-      </c>
-      <c r="K17" s="2"/>
+          <t>监测血压变化</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>避免与其他药物相互作用</t>
+        </is>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N17" s="2"/>
@@ -1082,14 +1086,10 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1103,34 +1103,42 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17.党员干部首先要把学习贯彻（  ）作为理论武装的重中之重，在学懂弄通做实上下苦功夫，以党的创新理论滋养初心、引领使命。</t>
+          <t>下列关于急性肾功能衰竭的治疗，错误的是。( )</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>习近平新时代中国特色社会主义思想</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>马克思主义</t>
+          <t>肾前性氮质血症者应首先寻找病因</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>毛泽东思想</t>
+          <t>肾后梗阻引起者应放置导尿管</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>邓小平理论</t>
-        </is>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+          <t>恶性高血压引起者应迅速把血压降至正常水平</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>RPGN应用免疫抑制疗法</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>早期的肾动脉血栓者应溶栓</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N18" s="2"/>
@@ -1139,17 +1147,13 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1160,34 +1164,42 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18.(多选)“两个维护”是保证全党团结统一、步调一致，带领全国各族人民决胜全面建成小康社会、奋力夺取新时代中国特色社会主义伟大胜利的根本政治保证。下面属于“两个维护”内容的是（  ）。</t>
+          <t>下列哪项是紧急血液透析的适应证.( )</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>坚决维护习近平总书记党中央的核心、全党的核心地位</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>坚决维护宪法的根本大法地位，全面依法治国</t>
+          <t>血钠105mmol/L</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>坚决维护中国特色社会主义理论体系，坚持理论自信</t>
+          <t>血钾6.6mmol/L</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>坚决维护党中央权威和集中统一领导</t>
-        </is>
-      </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+          <t>血氯111mmol/L</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>血钙1.75mmol/L</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>血pH7.30</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N19" s="2"/>
@@ -1196,14 +1208,10 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1217,34 +1225,42 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19.党的二十大报告指出，我们坚持走中国特色社会主义政治发展道路，全面发展全过程人民民主，社会主义民主政治制度化、规范化、程序化全面推进，人民当家作主更为扎实，（  ）总体格局基本形成。</t>
+          <t>少尿是指24小时尿量小于.( )</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>全面从严治党</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>全面依法治国</t>
+          <t>400ml</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>全面深化改革</t>
+          <t>70ml</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>全面建设社会主义现代化国家</t>
-        </is>
-      </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+          <t>200ml</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N20" s="2"/>
@@ -1253,14 +1269,10 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>一路长虹</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1274,34 +1286,38 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20.(单选)党的二十大报告指出，面对影响党长期执政、国家长治久安、人民幸福安康的突出矛盾和问题，党中央审时度势、果敢抉择，锐意进取、攻坚克难，团结带领全党全军全国各族人民撸起袖子加油干、风雨无阻向前行，义无反顾进行具有许多新的历史特点的（  ）。</t>
+          <t>透析患者的肾脏替代治疗方式不包括什么？( )</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>伟大斗争</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>伟大工程</t>
+          <t>血液透析</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>伟大事业</t>
+          <t>腹膜透析</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>伟大梦想</t>
-        </is>
-      </c>
-      <c r="K21" s="2"/>
+          <t>肾移植</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>灌流</t>
+        </is>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="2"/>
@@ -1310,14 +1326,10 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1331,34 +1343,38 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21.(单选)党的二十大报告指出，（  ）为新时代党和国家事业发展提供了根本遵循。</t>
+          <t>慢性肾脏病患者并发心力衰竭时，应如何处理？( )</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>用新时代中国特色社会主义思想武装头脑、指导实践、推动工作</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>全面加强党的领导</t>
+          <t>停用所有肾病治疗药物</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>以中国式现代化推进中华民族伟大复兴</t>
+          <t>加强心力衰竭的治疗</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>着力推进高质量发展</t>
-        </is>
-      </c>
-      <c r="K22" s="2"/>
+          <t>调整肾病治疗药物剂量</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>限制水分摄入</t>
+        </is>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N22" s="2"/>
@@ -1367,14 +1383,10 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1388,34 +1400,38 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22.(单选)党的二十大报告指出，我们对新时代党和国家事业发展作出科学完整的战略部署，明确“（  ）”总体布局和“（  ）”战略布局。</t>
+          <t>高钾血症的诊断标准是？( )</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>两个维护 四个现代化</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>四个现代化 两个维护</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>四个全面 五位一体</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>五位一体 四个全面</t>
-        </is>
-      </c>
-      <c r="K23" s="2"/>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N23" s="2"/>
@@ -1424,14 +1440,10 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1445,34 +1457,38 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23.(单选)党的二十大报告指出，我们贯彻总体国家安全观，国家安全领导体制和法治体系、战略体系、政策体系不断完善，在（  ）上寸步不让，以坚定的意志品质维护国家主权、安全、发展利益，国家安全得到全面加强。</t>
+          <t>导管出口处和隧道感染的原因错误的一项是？( )</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>领土问题</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>原则问题</t>
+          <t>导管出口方向不正确</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>主权问题</t>
+          <t>皮下隧道太短、涤纶套外露</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>内政问题</t>
-        </is>
-      </c>
-      <c r="K24" s="2"/>
+          <t>导管经常不牵拉</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>污染或未注意局部卫生</t>
+        </is>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N24" s="2"/>
@@ -1481,14 +1497,10 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1502,34 +1514,38 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24.(单选)党的二十大报告指出，我们确立党在新时代的强军目标，坚决把全军工作重心归正到（  ）上来，中国特色强军之路越走越宽广。</t>
+          <t>慢性肾脏病患者应用糖皮质激素时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>备战打仗</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>提升战斗力</t>
+          <t>长期使用</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>军事训练</t>
+          <t>监测血糖变化</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>军队改革</t>
-        </is>
-      </c>
-      <c r="K25" s="2"/>
+          <t>预防感染</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>监测肝功能</t>
+        </is>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N25" s="2"/>
@@ -1538,14 +1554,10 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1559,34 +1571,38 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25.(单选)党的二十大报告指出，我们深入推进全面从严治党，坚持打铁必须自身硬，从制定和落实（  ）开局破题，提出和落实新时代党的建设总要求。</t>
+          <t>对导管感染描述正确的是？( )</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>监督执纪“四种形态”</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>中国共产党纪律检查委员会工作条例</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要2周。</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>中央八项规定</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要3周。</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>三严三实主题教育</t>
-        </is>
-      </c>
-      <c r="K26" s="2"/>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要4周。</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要5周。</t>
+        </is>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N26" s="2"/>
@@ -1595,14 +1611,10 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="2"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1616,34 +1628,42 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26.(单选)党的二十大报告指出，拥有（  ）理论指导是我们党坚定信仰信念、把握历史主动的根本所在。</t>
+          <t>肾病综合征病人最常见体征是什么？( )</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>辩证唯物主义</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>马克思主义科学</t>
+          <t>疲乏无力</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>历史唯物主义</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>科学社会主义</t>
-        </is>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>高血脂</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N27" s="2"/>
@@ -1652,14 +1672,10 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="2"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1673,34 +1689,38 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27.(单选)党的二十大报告指出，十八大以来，我们党勇于进行理论探索和创新，以全新的视野深化对共产党执政规律、社会主义建设规律、人类社会发展规律的认识，取得重大理论创新成果，集中体现为（  ）。</t>
+          <t>参考最新指南，病程超过5年的1型糖尿病患者，每年应检查几次以评估UACR和GFR？( )</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>中国特色社会主义思想</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>马克思主义中国化理论</t>
+          <t>1次</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>新时代中国特色社会主义思想</t>
+          <t>2-3次</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>中国特色新发展思想</t>
-        </is>
-      </c>
-      <c r="K28" s="2"/>
+          <t>4次</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>4次以上</t>
+        </is>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N28" s="2"/>
@@ -1709,14 +1729,10 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1730,30 +1746,34 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29.(单选)“六个必须坚持”是新时代中国特色社会主义思想的世界观和方法论。“六个必须坚持”不包括（  ）。</t>
+          <t>狼疮性肾炎的患者如肾功能突然恶化，应考虑？( )</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>坚持自信自立</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>坚持系统观念</t>
+          <t>病理转型</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>坚持守正创新</t>
+          <t>病变活动</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>坚持中国共产党领导</t>
-        </is>
-      </c>
-      <c r="K29" s="2"/>
+          <t>急性肾小管坏死</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>以上情况均应考虑</t>
+        </is>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -1766,14 +1786,10 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="2"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1787,34 +1803,42 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30.党的全国代表大会（  ）年举办一次。</t>
+          <t>慢性肾脏病相关性瘙痒症（CKD-aP）的治疗方法包括哪些？( )</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>使用抗组胺药物</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>六</t>
+          <t>应用阿片受体拮抗剂</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>八</t>
-        </is>
-      </c>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+          <t>保持皮肤湿润</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>进行肾脏透析</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>仅通过饮食调整即可治愈</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A,B,C,D</t>
         </is>
       </c>
       <c r="N30" s="2"/>
@@ -1823,14 +1847,10 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1844,34 +1864,38 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31、必须更好发挥法治固根本、稳预期、利长远的保障作用，在法治轨道上（  ）。</t>
+          <t>依据瘙痒的起源、发病机制和皮损表现，瘙痒可分为哪几类？()</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全面建设社会主义现代化强国</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>全面建设社会主义国家</t>
+          <t>皮肤源性瘙痒</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>建设社会主义现代化强国</t>
+          <t>系统性瘙痒</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>建设社会主义现代化国家</t>
-        </is>
-      </c>
-      <c r="K31" s="2"/>
+          <t>神经源性瘙痒</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>精神障碍性瘙痒</t>
+        </is>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A,B,C,D</t>
         </is>
       </c>
       <c r="N31" s="2"/>
@@ -1880,14 +1904,10 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1901,30 +1921,34 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们创立了新时代中国特色社会主义思想，明确坚持和发展中国特色社会主义的基本方略，提出一系列治国理政（  ）。</t>
+          <t>慢性肾脏病患者合并肾性贫血时，其红细胞形态通常表现为？( )</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>新理念新思想新道路</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>中国智慧中国方案中国力量</t>
+          <t>球形红细胞</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>中国效率中国方案中国力量</t>
+          <t>椭圆形红细胞</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>新理念新思想新战略</t>
-        </is>
-      </c>
-      <c r="K32" s="2"/>
+          <t>靶形红细胞</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>正常形态红细胞</t>
+        </is>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -1937,14 +1961,10 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -1958,34 +1978,38 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>33、要加强人民当家作主制度保障，坚持和完善我国根本政治制度、基本政治制度、重要政治制度，拓展民主渠道，丰富民主形式，支持和保证人民通过（  ）行使国家权力。</t>
+          <t>哪项不是肾性贫血的临床表现？( )</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>人民代表大会</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>投票</t>
+          <t>面色苍白</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>选举</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>网络监督</t>
-        </is>
-      </c>
-      <c r="K33" s="2"/>
+          <t>心悸</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>黄疸</t>
+        </is>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" s="2"/>
@@ -1994,14 +2018,10 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2015,34 +2035,38 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34、习近平指出，从党的十八大开始，中国特色社会主义进入（  ）。</t>
+          <t>慢性肾脏病患者饮食疗法的目的是什么？( )</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>新征程</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>新阶段</t>
+          <t>控制蛋白质摄入</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>新时代</t>
+          <t>增加磷的摄入</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>新局面</t>
-        </is>
-      </c>
-      <c r="K34" s="2"/>
+          <t>维持营养平衡</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>减少钠盐摄入</t>
+        </is>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N34" s="2"/>
@@ -2051,14 +2075,10 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2072,34 +2092,38 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>35、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们坚持绿水青山就是金山银山的理念，坚持（  ）一体化保护和系统治理。</t>
+          <t>慢性肾功能不全患者出现贫血时，应首先考虑哪种可能性？( )</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>山水林湖草沙</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>山水林田湖草</t>
+          <t>缺铁性贫血</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>山水田湖草沙</t>
+          <t>溶血性贫血</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>山水林田湖草沙</t>
-        </is>
-      </c>
-      <c r="K35" s="2"/>
+          <t>肾性贫血</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>再生障碍性贫血</t>
+        </is>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N35" s="2"/>
@@ -2108,14 +2132,10 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B36" s="2"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2129,34 +2149,38 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>36、我们实行更加积极主动的开放战略，构建面向全球的高标准自由贸易区网络，加快推进自由贸易试验区、（  ）自由贸易港建设，共建“一带一路”成为深受欢迎的国际公共产品和国际合作平台。</t>
+          <t>关于慢性肾脏病的透析治疗，以下哪些说法正确？()</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>香港</t>
+          <t>透析可清除血液中的废物和多余液体</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>透析分为血液透析和腹膜透析</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="K36" s="2"/>
+          <t>腹膜透析中，透析液通过细管吸收废物和多余液体</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>透析可以完全治愈慢性肾脏病</t>
+        </is>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N36" s="2"/>
@@ -2165,14 +2189,10 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2186,34 +2206,38 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37、新时代十年的伟大变革，在党史、新中国史、改革开放史、社会主义发展史、中华民族发展史上具有（  ）</t>
+          <t>慢性肾脏病治疗中，如何纠正酸碱平衡失调？( )</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>划时代意义</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>跨时代意义</t>
+          <t>使用碱性药物</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>里程碑意义</t>
+          <t>限制酸性饮食</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>丰碑意义</t>
-        </is>
-      </c>
-      <c r="K37" s="2"/>
+          <t>纠正电解质紊乱</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>增加酸性药物摄入</t>
+        </is>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N37" s="2"/>
@@ -2222,14 +2246,10 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B38" s="2"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2243,29 +2263,25 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>38、五年来，我们坚持加强党的全面领导和（  ）集中统一领导，全力推进全面建成小康社会进程。</t>
+          <t>肾病综合征病人最突出的体征是什么？( )</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>各级政府</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>党中央</t>
+          <t>高血压</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>国务院</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>地方政府</t>
-        </is>
-      </c>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2" t="inlineStr">
@@ -2279,14 +2295,10 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B39" s="2"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2300,34 +2312,38 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>39、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，推进以（  ）为主体的自然保护地体系建设。</t>
+          <t>慢性肾脏病的治疗中，如何控制感染？( )</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>天然林</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>国家公园</t>
+          <t>使用广谱抗生素</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>生物多样性</t>
+          <t>根据病原体选择抗生素</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>湿地</t>
-        </is>
-      </c>
-      <c r="K39" s="2"/>
+          <t>长期使用抗生素预防感染</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>提高患者免疫力</t>
+        </is>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B,D</t>
         </is>
       </c>
       <c r="N39" s="2"/>
@@ -2336,14 +2352,10 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B40" s="2"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2357,34 +2369,42 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40、坚持多劳多得，鼓励勤劳致富，促进（  ），增加低收入者收入，扩大中等收入群体。</t>
+          <t>肾病综合征病人易自发形成血栓的主要原因是？( )</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>机会公平</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>机会平等</t>
+          <t>血管内皮易受损伤</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>机遇公平</t>
+          <t>红细胞增多</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>机遇平等</t>
-        </is>
-      </c>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
+          <t>组织因子释放</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>高脂血症</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>血小板增多</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N40" s="2"/>
@@ -2393,14 +2413,10 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>咫尺天涯</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B41" s="2"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2414,34 +2430,38 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>41、全方位夯实粮食安全根基，牢牢守住（  ）亩耕地红线。</t>
+          <t>肾病综合征病人24小时尿蛋白定量常为多少？( )</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>十七亿</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>十八亿</t>
+          <t>2.5g/d</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>十九亿</t>
+          <t>3.5g/d</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>二十亿</t>
-        </is>
-      </c>
-      <c r="K41" s="2"/>
+          <t>150mg/d</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1.5g/d</t>
+        </is>
+      </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N41" s="2"/>
@@ -2450,14 +2470,10 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B42" s="2"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2471,34 +2487,38 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42、面对国际局势急剧变化，我们保持战略定力，发扬斗争精神，在斗争中维护国家尊严和核心利益，牢牢掌握了我国（  ）。</t>
+          <t>肾病综合征严重水肿病人起身应慢，以防止什么？( )</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>发展和社会安全</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>发展和安全主动权</t>
+          <t>体位性低血压</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>发展和社会稳定</t>
+          <t>高血压</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>发展和领土安全</t>
-        </is>
-      </c>
-      <c r="K42" s="2"/>
+          <t>坠床</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>皮肤损伤</t>
+        </is>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N42" s="2"/>
@@ -2507,14 +2527,10 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B43" s="2"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2528,29 +2544,25 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>43、我们经过接续奋斗，实现了（  ）这个中华民族的千年梦想。</t>
+          <t>能确定肾病综合征的病理类型的检查项目是什么？( )</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>中国梦</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>小康</t>
+          <t>中段尿培养</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>强国</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>强军</t>
-        </is>
-      </c>
+          <t>尿蛋白定量</t>
+        </is>
+      </c>
+      <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2" t="inlineStr">
@@ -2564,14 +2576,10 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B44" s="2"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2585,34 +2593,38 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>44、党的二十大开幕的时间是（  ）。</t>
+          <t>关于慢性肾脏病的饮食疗法，以下哪些说法正确？( )</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2022年10月16日</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2022年10月17日</t>
+          <t>应限制蛋白质摄入</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2022年10月15日</t>
+          <t>应增加磷的摄入</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2022年10月18日</t>
-        </is>
-      </c>
-      <c r="K44" s="2"/>
+          <t>应控制钠盐摄入</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>应限制钾的摄入</t>
+        </is>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N44" s="2"/>
@@ -2621,14 +2633,10 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2642,34 +2650,38 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>45、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们坚持（  ）的理念。</t>
+          <t>糖尿病肾病最早期的临床表现是？( )</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>保卫母亲河</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>节能减排创造价值</t>
+          <t>大量白蛋白尿</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>天朗气清好生活</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>绿水青山就是金山银山</t>
-        </is>
-      </c>
-      <c r="K45" s="2"/>
+          <t>微量白蛋白尿</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>脓尿</t>
+        </is>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N45" s="2"/>
@@ -2678,14 +2690,10 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B46" s="2"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2699,34 +2707,38 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46、深化国企国资改革。落实国有科技型企业（  ）政策。</t>
+          <t>糖尿病肾病的英文及缩写为？( )</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>薪资调整</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>股权激励</t>
+          <t>Nephrotic Syndrome(NS)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>股权和分红激励</t>
+          <t>Diabetic Kidney Disease(DKD)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>分红激励</t>
-        </is>
-      </c>
-      <c r="K46" s="2"/>
+          <t>Systemic Lupus Erythematosus(SLE)</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease(CKD)</t>
+        </is>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N46" s="2"/>
@@ -2735,14 +2747,10 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B47" s="2"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2756,34 +2764,38 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，拥有（  ）是我们党坚定信仰信念、把握历史主动的根本所在。</t>
+          <t>慢性肾脏病患者使用利尿剂时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>科学社会主义</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>坚持人民主体地位</t>
+          <t>监测电解质平衡</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>马克思主义科学理论指导</t>
+          <t>长期使用利尿剂</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>不断推进自我革命</t>
-        </is>
-      </c>
-      <c r="K47" s="2"/>
+          <t>监测血压变化</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>避免与其他药物相互作用</t>
+        </is>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N47" s="2"/>
@@ -2792,14 +2804,10 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B48" s="2"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2813,34 +2821,42 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>48、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，加快建设世界重要人才中心和创新高地，着力形成人才国际竞争的（  ）优势。</t>
+          <t>下列关于急性肾功能衰竭的治疗，错误的是。( )</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>全面</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>比较</t>
+          <t>肾前性氮质血症者应首先寻找病因</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>绝对</t>
+          <t>肾后梗阻引起者应放置导尿管</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>最强</t>
-        </is>
-      </c>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
+          <t>恶性高血压引起者应迅速把血压降至正常水平</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>RPGN应用免疫抑制疗法</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>早期的肾动脉血栓者应溶栓</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N48" s="2"/>
@@ -2849,14 +2865,10 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2870,34 +2882,42 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>49、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，治国有常，（  ）为本。</t>
+          <t>下列哪项是紧急血液透析的适应证.( )</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>利民</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>农民</t>
+          <t>血钠105mmol/L</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>领导</t>
+          <t>血钾6.6mmol/L</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>大众</t>
-        </is>
-      </c>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
+          <t>血氯111mmol/L</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>血钙1.75mmol/L</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>血pH7.30</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N49" s="2"/>
@@ -2906,14 +2926,10 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2927,34 +2943,42 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>50、（  ）是国家安全的根本。</t>
+          <t>少尿是指24小时尿量小于.( )</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>经济安全</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>政治安全</t>
+          <t>400ml</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>生态安全</t>
+          <t>70ml</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>生物安全</t>
-        </is>
-      </c>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
+          <t>200ml</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N50" s="2"/>
@@ -2963,14 +2987,10 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -2984,34 +3004,38 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>51、加大财政资源统筹力度，积极盘活各类资金资产，稳妥化解（  ）。</t>
+          <t>透析患者的肾脏替代治疗方式不包括什么？( )</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>金融危机</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>债务风险</t>
+          <t>血液透析</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>存量隐性债务</t>
+          <t>腹膜透析</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>地方债务</t>
-        </is>
-      </c>
-      <c r="K51" s="2"/>
+          <t>肾移植</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>灌流</t>
+        </is>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N51" s="2"/>
@@ -3020,14 +3044,10 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3041,34 +3061,38 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>52、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们要办好人民满意的教育，全面贯彻党的教育方针，落实立德树人根本任务，培养（  ）的社会主义建设者和接班人。</t>
+          <t>慢性肾脏病患者并发心力衰竭时，应如何处理？( )</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>又红又专</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>四有新人</t>
+          <t>停用所有肾病治疗药物</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>德智体美劳全面发展</t>
+          <t>加强心力衰竭的治疗</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>德才兼备</t>
-        </is>
-      </c>
-      <c r="K52" s="2"/>
+          <t>调整肾病治疗药物剂量</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>限制水分摄入</t>
+        </is>
+      </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N52" s="2"/>
@@ -3077,14 +3101,10 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3098,34 +3118,38 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>53、推进（  ）建设，推动工业固体废物和再生资源规模化、高值化利用。</t>
+          <t>高钾血症的诊断标准是？( )</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>生态产品交易中心</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>生态保护补偿机制</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>工业资源综合利用基地</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>森林质量精准提升工程</t>
-        </is>
-      </c>
-      <c r="K53" s="2"/>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N53" s="2"/>
@@ -3134,14 +3158,10 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B54" s="2"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3155,30 +3175,34 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>54、全党同志务必不忘初心、牢记使命，务必谦虚谨慎、艰苦奋斗，务必（  ），坚定历史自信，增强历史主动，谱写新时代中国特色社会主义更加绚丽的华章。</t>
+          <t>导管出口处和隧道感染的原因错误的一项是？( )</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>勇于斗争、善于斗争</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>敢于斗争、乐于斗争</t>
+          <t>导管出口方向不正确</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>敢于斗争、善于斗争</t>
+          <t>皮下隧道太短、涤纶套外露</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>勇于斗争、乐于斗争</t>
-        </is>
-      </c>
-      <c r="K54" s="2"/>
+          <t>导管经常不牵拉</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>污染或未注意局部卫生</t>
+        </is>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3191,14 +3215,10 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3212,34 +3232,38 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>55、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，加强同（  ）的团结合作。</t>
+          <t>慢性肾脏病患者应用糖皮质激素时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>广大群众</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>非政界人士</t>
+          <t>长期使用</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>国内外人士</t>
+          <t>监测血糖变化</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>民主党派和无党派人士</t>
-        </is>
-      </c>
-      <c r="K55" s="2"/>
+          <t>预防感染</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>监测肝功能</t>
+        </is>
+      </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N55" s="2"/>
@@ -3248,14 +3272,10 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B56" s="2"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3269,34 +3289,38 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>56、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，必须牢固树立和践行（  ）的理念。</t>
+          <t>对导管感染描述正确的是？( )</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>绿水青山就是金山银山</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>只要绿水青山不要金山银山</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要2周。</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>金山银山就是绿水青山</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要3周。</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>既要绿水青山又要金山银山</t>
-        </is>
-      </c>
-      <c r="K56" s="2"/>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要4周。</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要5周。</t>
+        </is>
+      </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N56" s="2"/>
@@ -3305,14 +3329,10 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B57" s="2"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3326,34 +3346,42 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>57、中国坚定奉行（  ）的和平外交政策。</t>
+          <t>肾病综合征病人最常见体征是什么？( )</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>互帮互助</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>不结盟</t>
+          <t>疲乏无力</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>独立自主</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>互不干涉</t>
-        </is>
-      </c>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>高血脂</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N57" s="2"/>
@@ -3362,14 +3390,10 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B58" s="2"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3383,34 +3407,38 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>58、坚持（  ）在我国现代化建设全局中的核心地位。</t>
+          <t>参考最新指南，病程超过5年的1型糖尿病患者，每年应检查几次以评估UACR和GFR？( )</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>人才</t>
+          <t>1次</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>2-3次</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>创新</t>
-        </is>
-      </c>
-      <c r="K58" s="2"/>
+          <t>4次</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>4次以上</t>
+        </is>
+      </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N58" s="2"/>
@@ -3419,14 +3447,10 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>抢答题</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B59" s="2"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3440,34 +3464,38 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>59、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，十年来，我们对新时代党和国家事业发展作出科学完整的战略部署，确定（  ）工作总基调。</t>
+          <t>狼疮性肾炎的患者如肾功能突然恶化，应考虑？( )</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>稳中求进</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>稳中求快</t>
+          <t>病理转型</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>进中求快</t>
+          <t>病变活动</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>进中求稳</t>
-        </is>
-      </c>
-      <c r="K59" s="2"/>
+          <t>急性肾小管坏死</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>以上情况均应考虑</t>
+        </is>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N59" s="2"/>
@@ -3476,14 +3504,10 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3497,42 +3521,42 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>60、习近平总书记在党的二十大报告提出“三个务必”是指（  ）。</t>
+          <t>慢性肾脏病相关性瘙痒症（CKD-aP）的治疗方法包括哪些？( )</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>务必不忘初心、牢记使命，务必谦虚谨慎、艰苦奋斗，务必敢于斗争、善于斗争</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>务必保持清醒头脑、务必发扬艰苦作风、务必迎接风险挑战</t>
+          <t>使用抗组胺药物</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>务必放下架子接地气、务必扑下身子转作风、务必扎下根子办实事</t>
+          <t>应用阿片受体拮抗剂</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>以上答案都不对</t>
+          <t>保持皮肤湿润</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>进行肾脏透析</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>仅通过饮食调整即可治愈</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A,B,C,D</t>
         </is>
       </c>
       <c r="N60" s="2"/>
@@ -3541,14 +3565,10 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B61" s="2"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3562,34 +3582,38 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>61、我国的分配制度是（  ）。</t>
+          <t>依据瘙痒的起源、发病机制和皮损表现，瘙痒可分为哪几类？()</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>按劳分配为主体、按需分配为辅</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>按需分配为主体、按劳分配为辅</t>
+          <t>皮肤源性瘙痒</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>按劳分配为主体、多种分配方式并存</t>
+          <t>系统性瘙痒</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>按需分配为主体、多种分配方式并存</t>
-        </is>
-      </c>
-      <c r="K61" s="2"/>
+          <t>神经源性瘙痒</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>精神障碍性瘙痒</t>
+        </is>
+      </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A,B,C,D</t>
         </is>
       </c>
       <c r="N61" s="2"/>
@@ -3598,14 +3622,10 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B62" s="2"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3619,34 +3639,38 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>62、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）原则，把新时代好干部标准落到实处。</t>
+          <t>慢性肾脏病患者合并肾性贫血时，其红细胞形态通常表现为？( )</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>党管人才</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>以德为先</t>
+          <t>球形红细胞</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>党管干部</t>
+          <t>椭圆形红细胞</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>德才兼备</t>
-        </is>
-      </c>
-      <c r="K62" s="2"/>
+          <t>靶形红细胞</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>正常形态红细胞</t>
+        </is>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N62" s="2"/>
@@ -3655,14 +3679,10 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3676,34 +3696,38 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>63、全党必须牢记，全面从严治党永远在路上，（  ）永远在路上。</t>
+          <t>哪项不是肾性贫血的临床表现？( )</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>党的自我革命</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>党的自我革新</t>
+          <t>面色苍白</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>党的自我完善</t>
+          <t>乏力</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>党的自我提高</t>
-        </is>
-      </c>
-      <c r="K63" s="2"/>
+          <t>心悸</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>黄疸</t>
+        </is>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="2"/>
@@ -3712,14 +3736,10 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B64" s="2"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3733,34 +3753,38 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>64、全面依法治国是（  ）的一场深刻革命，关系党执政兴国，关系人民幸福安康，关系党和国家长治久安。</t>
+          <t>慢性肾脏病患者饮食疗法的目的是什么？( )</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>国家治理</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>顶层设计</t>
+          <t>控制蛋白质摄入</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>治理能力</t>
+          <t>增加磷的摄入</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>法治社会</t>
-        </is>
-      </c>
-      <c r="K64" s="2"/>
+          <t>维持营养平衡</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>减少钠盐摄入</t>
+        </is>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N64" s="2"/>
@@ -3769,14 +3793,10 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B65" s="2"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3790,34 +3810,38 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>65、不断谱写马克思主义中国化时代化新篇章，是当代中国共产党人的庄严（  ）。</t>
+          <t>慢性肾功能不全患者出现贫血时，应首先考虑哪种可能性？( )</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>政治责任</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>重要任务</t>
+          <t>缺铁性贫血</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>重点工作</t>
+          <t>溶血性贫血</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>历史责任</t>
-        </is>
-      </c>
-      <c r="K65" s="2"/>
+          <t>肾性贫血</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>再生障碍性贫血</t>
+        </is>
+      </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N65" s="2"/>
@@ -3826,14 +3850,10 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B66" s="2"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3847,34 +3867,38 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>66、健全资本市场功能，提高（  ）融资比重。</t>
+          <t>关于慢性肾脏病的透析治疗，以下哪些说法正确？()</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>间接</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>直接</t>
+          <t>透析可清除血液中的废物和多余液体</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>透析分为血液透析和腹膜透析</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>外部</t>
-        </is>
-      </c>
-      <c r="K66" s="2"/>
+          <t>腹膜透析中，透析液通过细管吸收废物和多余液体</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>透析可以完全治愈慢性肾脏病</t>
+        </is>
+      </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N66" s="2"/>
@@ -3883,14 +3907,10 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B67" s="2"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3904,34 +3924,38 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>67、全心全意依靠（  ），健全以职工代表大会为基本形式的企事业单位民主管理制度，维护职工合法权益。</t>
+          <t>慢性肾脏病治疗中，如何纠正酸碱平衡失调？( )</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>群体组织</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>基层党组织</t>
+          <t>使用碱性药物</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>群团组织</t>
+          <t>限制酸性饮食</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>工人阶级</t>
-        </is>
-      </c>
-      <c r="K67" s="2"/>
+          <t>纠正电解质紊乱</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>增加酸性药物摄入</t>
+        </is>
+      </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A,B,C</t>
         </is>
       </c>
       <c r="N67" s="2"/>
@@ -3940,14 +3964,10 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B68" s="2"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -3961,34 +3981,30 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>68、发展壮大医疗卫生队伍，把工作重点放在（  ）。</t>
+          <t>肾病综合征病人最突出的体征是什么？( )</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>乡村和社区</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>农村和居委会</t>
+          <t>高血压</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>农村和社区</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>农村和小区</t>
-        </is>
-      </c>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N68" s="2"/>
@@ -3997,14 +4013,10 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B69" s="2"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4018,34 +4030,38 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>69、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化是（  ）的现代化。</t>
+          <t>慢性肾脏病的治疗中，如何控制感染？( )</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>全面建成小康社会</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>社会主义的现代化</t>
+          <t>使用广谱抗生素</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>实现中华民族伟大复兴</t>
+          <t>根据病原体选择抗生素</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>全体人民共同富裕</t>
-        </is>
-      </c>
-      <c r="K69" s="2"/>
+          <t>长期使用抗生素预防感染</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>提高患者免疫力</t>
+        </is>
+      </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B,D</t>
         </is>
       </c>
       <c r="N69" s="2"/>
@@ -4054,14 +4070,10 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B70" s="2"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4075,34 +4087,42 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>70、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化的本质要求是：实现（  ）发展。</t>
+          <t>肾病综合征病人易自发形成血栓的主要原因是？( )</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>高水平</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>血管内皮易受损伤</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>高效</t>
+          <t>红细胞增多</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>高质量</t>
-        </is>
-      </c>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
+          <t>组织因子释放</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>高脂血症</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>血小板增多</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N70" s="2"/>
@@ -4111,14 +4131,10 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4132,34 +4148,38 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>71、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国式现代化的本质要求是：推动构建人类命运共同体，创造（  ）。</t>
+          <t>肾病综合征病人24小时尿蛋白定量常为多少？( )</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>人类文明新业态</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>人类文明新形态</t>
+          <t>2.5g/d</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>人精神文明新形态</t>
+          <t>3.5g/d</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>政治文明新形态</t>
-        </is>
-      </c>
-      <c r="K71" s="2"/>
+          <t>150mg/d</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>1.5g/d</t>
+        </is>
+      </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N71" s="2"/>
@@ -4168,14 +4188,10 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4189,34 +4205,38 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>72、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，建设（  ）的高素质干部队伍。</t>
+          <t>肾病综合征严重水肿病人起身应慢，以防止什么？( )</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>德才兼备</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>通才与专才相结合</t>
+          <t>体位性低血压</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>革命化、年轻化、知识化、专业化</t>
+          <t>高血压</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>堪当民族复兴重任</t>
-        </is>
-      </c>
-      <c r="K72" s="2"/>
+          <t>坠床</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>皮肤损伤</t>
+        </is>
+      </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N72" s="2"/>
@@ -4225,14 +4245,10 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B73" s="2"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4246,34 +4262,30 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>73、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）对外开放。</t>
+          <t>能确定肾病综合征的病理类型的检查项目是什么？( )</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>全方位</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>全天候</t>
+          <t>中段尿培养</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>全面</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>高水平</t>
-        </is>
-      </c>
+          <t>尿蛋白定量</t>
+        </is>
+      </c>
+      <c r="J73" s="2"/>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N73" s="2"/>
@@ -4282,14 +4294,10 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B74" s="2"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4303,34 +4311,38 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>74、（  ）是社会主义的生命，是全面建设社会主义现代化国家的应有之义。</t>
+          <t>关于慢性肾脏病的饮食疗法，以下哪些说法正确？( )</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>人民代表大会</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>社会民主</t>
+          <t>应限制蛋白质摄入</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>国家富强</t>
+          <t>应增加磷的摄入</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>人民民主</t>
-        </is>
-      </c>
-      <c r="K74" s="2"/>
+          <t>应控制钠盐摄入</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>应限制钾的摄入</t>
+        </is>
+      </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N74" s="2"/>
@@ -4339,14 +4351,10 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B75" s="2"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4360,34 +4368,38 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>75、十九大以来的五年，是（  ）的五年。</t>
+          <t>糖尿病肾病最早期的临床表现是？( )</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>极不寻常、极不平凡</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>党和国家发展进程中极不平凡</t>
+          <t>大量白蛋白尿</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>我们经受住各种困难和风险考验、夺取全面建设小康社会新胜利</t>
+          <t>血尿</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>不平凡</t>
-        </is>
-      </c>
-      <c r="K75" s="2"/>
+          <t>微量白蛋白尿</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>脓尿</t>
+        </is>
+      </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N75" s="2"/>
@@ -4396,14 +4408,10 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B76" s="2"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4417,34 +4425,38 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>76、没有坚实的（  ）基础，就不可能全面建成社会主义现代化强国。</t>
+          <t>糖尿病肾病的英文及缩写为？( )</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>政治文化</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>经济产业</t>
+          <t>Nephrotic Syndrome(NS)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>物质技术</t>
+          <t>Diabetic Kidney Disease(DKD)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>自然资源</t>
-        </is>
-      </c>
-      <c r="K76" s="2"/>
+          <t>Systemic Lupus Erythematosus(SLE)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease(CKD)</t>
+        </is>
+      </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N76" s="2"/>
@@ -4453,14 +4465,10 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>20分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B77" s="2"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4474,34 +4482,38 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>77、要坚持党的领导、人民当家作主、依法治国（  ）。</t>
+          <t>慢性肾脏病患者使用利尿剂时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>辩证统一</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>有机统一</t>
+          <t>监测电解质平衡</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>相互协调</t>
+          <t>长期使用利尿剂</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>协调统一</t>
-        </is>
-      </c>
-      <c r="K77" s="2"/>
+          <t>监测血压变化</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>避免与其他药物相互作用</t>
+        </is>
+      </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A,C,D</t>
         </is>
       </c>
       <c r="N77" s="2"/>
@@ -4510,14 +4522,10 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B78" s="2"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4531,31 +4539,39 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>78、治国有常，利民为本。（  ）是立党为公、执政为民的本质要求。</t>
+          <t>下列关于急性肾功能衰竭的治疗，错误的是。( )</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>为民请命</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>为民谋福</t>
+          <t>肾前性氮质血症者应首先寻找病因</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>为民造福</t>
+          <t>肾后梗阻引起者应放置导尿管</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>为民解难</t>
-        </is>
-      </c>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
+          <t>恶性高血压引起者应迅速把血压降至正常水平</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>RPGN应用免疫抑制疗法</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>早期的肾动脉血栓者应溶栓</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>C</t>
@@ -4567,14 +4583,10 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B79" s="2"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4588,34 +4600,42 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>79、全党必须牢记，坚持（  ）是坚持和发展中国特色社会主义的必由之路。</t>
+          <t>下列哪项是紧急血液透析的适应证.( )</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>群众路线</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>人民民主</t>
+          <t>血钠105mmol/L</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>以人民为中心</t>
+          <t>血钾6.6mmol/L</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>党的全面领导</t>
-        </is>
-      </c>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
+          <t>血氯111mmol/L</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>血钙1.75mmol/L</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>血pH7.30</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N79" s="2"/>
@@ -4624,14 +4644,10 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B80" s="2"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4645,34 +4661,42 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>80、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，（  ）是实现中华民族伟大复兴的必由之路。</t>
+          <t>少尿是指24小时尿量小于.( )</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>团结奋斗</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>中国特色社会主义</t>
+          <t>400ml</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>新发展理念</t>
+          <t>70ml</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>全面从严治党</t>
-        </is>
-      </c>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
+          <t>200ml</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N80" s="2"/>
@@ -4681,14 +4705,10 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B81" s="2"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4702,34 +4722,38 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>81、习近平总书记在党的二十大报告中指出：“（  ）是立党为公、执政为民的本质要求。”</t>
+          <t>透析患者的肾脏替代治疗方式不包括什么？( )</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>为民造福</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>为民服务</t>
+          <t>血液透析</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>为民着想</t>
+          <t>腹膜透析</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>为民干事</t>
-        </is>
-      </c>
-      <c r="K81" s="2"/>
+          <t>肾移植</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>灌流</t>
+        </is>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N81" s="2"/>
@@ -4738,14 +4762,10 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B82" s="2"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4759,34 +4779,38 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>82、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，坚持（  ）是坚持和发展中国特色社会主义的必由之路。</t>
+          <t>慢性肾脏病患者并发心力衰竭时，应如何处理？( )</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>党的全面领导</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>全面从严治党</t>
+          <t>停用所有肾病治疗药物</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>以人民为中心</t>
+          <t>加强心力衰竭的治疗</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>新发展理念</t>
-        </is>
-      </c>
-      <c r="K82" s="2"/>
+          <t>调整肾病治疗药物剂量</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>限制水分摄入</t>
+        </is>
+      </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N82" s="2"/>
@@ -4795,14 +4819,10 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B83" s="2"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4816,30 +4836,34 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>83、（  ）大，（  ）全会提出的“十个明确”、“十四个坚持”、“十三个方面成就”概括了这一思想的主要内容，必须长期坚持并不断丰富发展。</t>
+          <t>高钾血症的诊断标准是？( )</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>十九 十九届六中</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>十九 十九届五中</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>十八 十八届六中</t>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>十八 十八届五中</t>
-        </is>
-      </c>
-      <c r="K83" s="2"/>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
+        </is>
+      </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -4852,14 +4876,10 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4873,34 +4893,38 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>84、全面依法治国的重点任务和主体工程是（  ）。</t>
+          <t>导管出口处和隧道感染的原因错误的一项是？( )</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>法治国家</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>法治政府</t>
+          <t>导管出口方向不正确</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>法治社会</t>
+          <t>皮下隧道太短、涤纶套外露</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>法治公民</t>
-        </is>
-      </c>
-      <c r="K84" s="2"/>
+          <t>导管经常不牵拉</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>污染或未注意局部卫生</t>
+        </is>
+      </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N84" s="2"/>
@@ -4909,14 +4933,10 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B85" s="2"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4930,34 +4950,38 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>85、到（  ）年，我国农村基本具备现代生活条件。</t>
+          <t>慢性肾脏病患者应用糖皮质激素时，应注意什么？( )</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>二O二五年</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>二O五O年</t>
+          <t>长期使用</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>二O三O年</t>
+          <t>监测血糖变化</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>二O三五年</t>
-        </is>
-      </c>
-      <c r="K85" s="2"/>
+          <t>预防感染</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>监测肝功能</t>
+        </is>
+      </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B,C,D</t>
         </is>
       </c>
       <c r="N85" s="2"/>
@@ -4966,14 +4990,10 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B86" s="2"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -4987,30 +5007,34 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>86、习近平总书记代表第十九届中央委员会向大会作的报告共分（  ）部分。</t>
+          <t>对导管感染描述正确的是？( )</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>十四</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>十五</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要2周。</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>十六</t>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要3周。</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>十七</t>
-        </is>
-      </c>
-      <c r="K86" s="2"/>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要4周。</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要5周。</t>
+        </is>
+      </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5023,14 +5047,10 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B87" s="2"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -5044,31 +5064,39 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>87、为民造福是立党为公、执政为民的（  ）。</t>
+          <t>肾病综合征病人最常见体征是什么？( )</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>根本要求</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>基本要求</t>
+          <t>疲乏无力</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>首要要求</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>本质要求</t>
-        </is>
-      </c>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
+          <t>高血压</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>水肿</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>高血脂</t>
+        </is>
+      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
           <t>D</t>
@@ -5080,14 +5108,10 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B88" s="2"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -5101,30 +5125,34 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>88、维护社会公平正义的最后一道防线是（  ）。</t>
+          <t>参考最新指南，病程超过5年的1型糖尿病患者，每年应检查几次以评估UACR和GFR？( )</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>公正司法</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>严格执法</t>
+          <t>1次</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>科学立法</t>
+          <t>2-3次</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>全民守法</t>
-        </is>
-      </c>
-      <c r="K88" s="2"/>
+          <t>4次</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>4次以上</t>
+        </is>
+      </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5137,14 +5165,10 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -5158,34 +5182,38 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>89、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，中国坚持（  ），推动建设一个清洁美丽的世界。</t>
+          <t>狼疮性肾炎的患者如肾功能突然恶化，应考虑？( )</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>循环发展</t>
+          <t>单选题</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>创新发展</t>
+          <t>病理转型</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>绿色低碳</t>
+          <t>病变活动</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>简约适度</t>
-        </is>
-      </c>
-      <c r="K89" s="2"/>
+          <t>急性肾小管坏死</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>以上情况均应考虑</t>
+        </is>
+      </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N89" s="2"/>
@@ -5194,14 +5222,10 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B90" s="2"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>单选题</t>
@@ -5215,1235 +5239,46 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>90、发展是党执政兴国的第一（  ）。</t>
+          <t>慢性肾脏病相关性瘙痒症（CKD-aP）的治疗方法包括哪些？( )</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>任务</t>
+          <t>多选题</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>要务</t>
+          <t>使用抗组胺药物</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>使命</t>
+          <t>应用阿片受体拮抗剂</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>责任</t>
-        </is>
-      </c>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
+          <t>保持皮肤湿润</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>进行肾脏透析</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>仅通过饮食调整即可治愈</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A,B,C,D</t>
         </is>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>91、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，江山就是人民，人民就是江山。中国共产党领导人民打江山、守江山，守的是（  ）。</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>国泰民安</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>人民的心</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>公平自由</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>人民民主</t>
-        </is>
-      </c>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>92、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，我们贯彻（  ）。</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>国家安全观</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>总体安全观</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>国家安全总体观</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>总体国家安全观</t>
-        </is>
-      </c>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>93、健全（  ）的社会治理制度，提升社会治理效能。</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>共建共治共用</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>共建共治共享</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>共聚共治共享</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>共建共治共有</t>
-        </is>
-      </c>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>94、深入推进全面（  ），坚持打铁必须自身硬，提出和落实新时代党的建设总要求。</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>依法治党</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>依法治国</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>从严治党</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>从严治国</t>
-        </is>
-      </c>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>95、（  ）是我们立党立国、兴党兴国的根本指导思想。</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>马克思主义</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>毛泽东思想</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>邓小平理论</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>“三个代表”重要思想</t>
-        </is>
-      </c>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>96、（  ）是历史的创造者。</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>群众</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>公民</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>党员</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>人民群众</t>
-        </is>
-      </c>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>97、全党必须牢记，全面（  ）永远在路上，党的（  ）永远在路上。</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>依法治党 自我革命</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>依法治党 自我革新</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>从严治党 自我革命</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>从严治党 自我革新</t>
-        </is>
-      </c>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>98、2022年10月16日，习近平在中国共产党第二十次全国代表大会上的报告指出，深入开展社会主义核心价值观宣传教育，深化爱国主义、集体主义、社会主义教育，着力培养（  ）。</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>实现中国特色社会主义共同理想的新人</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>实现共产主义远大理想的时代新人</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>担当民族复兴大任的时代新人</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>有担当、有理想、有本领的时代新人</t>
-        </is>
-      </c>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>99、习近平总书记在党的二十大报告中指出，党用伟大奋斗创造了百年伟业，也一定能用（  ）创造新的伟业。</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>奋斗</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>伟大奋斗</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>新的伟大奋斗</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>团结奋斗</t>
-        </is>
-      </c>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>100、习近平总书记在党的二十大报告中指出，走过百年奋斗历程的中国共产党在革命性锻造中更加坚强有力，党的政治领导力、思想引领力、群众组织力、社会号召力显著增强，党同人民群众始终保持血肉联系，中国共产党在世界形势深刻变化的历史进程中始终走在（  ），在应对国内外各种风险和考验的历史进程中始终成为全国人民的主心骨，在坚持和发展中国特色社会主义的历史进程中始终成为坚强领导核心。</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>时代前列</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>时代前沿</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>历史前列</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>历史前沿</t>
-        </is>
-      </c>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1、必须坚持在发展中保障和改善民生，鼓励（  ）创造美好生活，不断实现人民对美好生活的向往。</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>团结奋斗</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>共同努力</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>共同奋斗</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>踔厉奋进</t>
-        </is>
-      </c>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2、以铸牢中华民族共同体意识为主线，加强和改进党的（  ）。</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>民族工作</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>民族团结工作</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>宗教工作</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>综治工作</t>
-        </is>
-      </c>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>3、加强和改进侨务工作，形成共同致力民族复兴的（  ）。</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>核心力量</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>重要力量</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>强大力量</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>关键力量</t>
-        </is>
-      </c>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>4、党的二十大报告中指出，（  ）是党执政兴国的第一要务。</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>法治</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>安全</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>发展</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>稳定</t>
-        </is>
-      </c>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>5、（  ）是实现中华民族伟大复兴的必由之路。</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>坚持党的全面领导</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>中国特色社会主义</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>团结奋斗</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>全面从严治党</t>
-        </is>
-      </c>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>6、构筑法治国家的基础是（  ）。</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>法治国家</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>法治政府</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>法治社会</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>法治公民</t>
-        </is>
-      </c>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>7、必须增强忧患意识，坚持（  ），做到居安思危、未雨绸缪，准备经受风高浪急甚至惊涛骇浪的重大考验。</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>底线思维</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>辩证思维</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>创新思维</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>法治思维</t>
-        </is>
-      </c>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>8、坚持和完善“（  ）”是新时代党解决台湾问题总体方略的根本保证。</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>和平发展</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>一国两制</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>民族区域自治</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>九二共识</t>
-        </is>
-      </c>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>9、党的二十大报告中指出，实施（  ），推进各类资源节约集约利用，加快构建废弃物循环利用体系。</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>全面节约战略</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>深度节约战略</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>节约优先战略</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>资源循环利用战略</t>
-        </is>
-      </c>
-      <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>10、我国基本实现社会主义现代化的时间节点是（  ）。</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>2020-2035年</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>2022-2035年</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>2025-2035年</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>2016-2022年</t>
-        </is>
-      </c>
-      <c r="K110" s="2"/>
-      <c r="L110" s="2"/>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>4.1.1</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>共答题</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>单选题</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>11、发展壮大医疗卫生队伍，把工作重点放在（  ）。</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>城市和街道</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>城市和农村</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>农村和街道</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>农村和社区</t>
-        </is>
-      </c>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fx-server/资源/题库/题目.xlsx
+++ b/fx-server/资源/题库/题目.xlsx
@@ -101,12 +101,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阶段编号</t>
+          <t>环节编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>阶段名称</t>
+          <t>环节名称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -171,7 +171,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>所属题组</t>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -283,7 +283,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>D哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )哪项不是肾性贫血的临床表现？( )</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="2"/>
@@ -479,11 +479,13 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="O7" s="2" t="n">
+        <v>1002.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1217,7 +1219,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？透析患者的肾脏替代治疗方式不包括什么？</t>
         </is>
       </c>
       <c r="N21" s="2"/>
@@ -3936,7 +3938,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>C1231231</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N72" s="2"/>
@@ -4925,7 +4927,7 @@
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4936,34 +4938,18 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>慢性肾脏病患者使用利尿剂时，应注意什么？( )</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>监测电解质平衡</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>长期使用利尿剂</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>监测血压变化</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>避免与其他药物相互作用</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1284 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>ACD</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；2、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N91" s="2"/>
@@ -4978,7 +4964,7 @@
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4989,38 +4975,20 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>下列关于急性肾功能衰竭的治疗，错误的是。( )</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>肾前性氮质血症者应首先寻找病因</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>肾后梗阻引起者应放置导尿管</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>恶性高血压引起者应迅速把血压降至正常水平</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>RPGN应用免疫抑制疗法</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>早期的肾动脉血栓者应溶栓</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。
+  入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1285 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。
+  心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；3、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N92" s="2"/>
@@ -5035,7 +5003,7 @@
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5046,38 +5014,18 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>下列哪项是紧急血液透析的适应证.( )</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>血钠105mmol/L</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>血钾6.6mmol/L</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>血氯111mmol/L</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>血钙1.75mmol/L</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>血pH7.30</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1286 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；4、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N93" s="2"/>
@@ -5092,7 +5040,7 @@
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5103,34 +5051,18 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>透析患者的肾脏替代治疗方式不包括什么？( )</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>血液透析</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>腹膜透析</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>肾移植</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>灌流</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1287 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；5、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N94" s="2"/>
@@ -5145,7 +5077,7 @@
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5156,34 +5088,18 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>慢性肾脏病患者并发心力衰竭时，应如何处理？( )</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>停用所有肾病治疗药物</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>加强心力衰竭的治疗</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>调整肾病治疗药物剂量</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>限制水分摄入</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1288 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；6、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N95" s="2"/>
@@ -5198,7 +5114,7 @@
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5209,34 +5125,18 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>高钾血症的诊断标准是？( )</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>CKD患者血清钾浓度≥5.0 mmol/L，诊断为高钾血症</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1289 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；7、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N96" s="2"/>
@@ -5251,7 +5151,7 @@
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5262,34 +5162,18 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>导管出口处和隧道感染的原因错误的一项是？( )</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>导管出口方向不正确</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>皮下隧道太短、涤纶套外露</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>导管经常不牵拉</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>污染或未注意局部卫生</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1290 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；8、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N97" s="2"/>
@@ -5304,7 +5188,7 @@
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5315,34 +5199,18 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>慢性肾脏病患者应用糖皮质激素时，应注意什么？( )</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>长期使用</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>监测血糖变化</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>预防感染</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>监测肝功能</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1291 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>BCD</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；9、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N98" s="2"/>
@@ -5357,7 +5225,7 @@
       <c r="B99" s="2"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5368,34 +5236,18 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>对导管感染描述正确的是？( )</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要2周。</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要3周。</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要4周。</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>抗感染治疗应持续至导管出口处完全恢复正常，通常至少需要2周；铜绿假单胞菌出口处感染治疗通常需要5周。</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1292 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；10、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N99" s="2"/>
@@ -5410,7 +5262,7 @@
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5421,38 +5273,18 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>肾病综合征病人最常见体征是什么？( )</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>疲乏无力</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>头晕</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>高血压</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>水肿</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>高血脂</t>
-        </is>
-      </c>
+          <t>该患者平时血红蛋白维持在100g/L左右，2021年2月时发现血红蛋白下降至71 g/L，予调整促红素方案，由“2000单位，每周3次”改为“10000单位，每周1次”，3月后患者血红蛋白升至80g/L，予再次调整促红素剂量为“10000单位，每周2次”，3月后患者血红蛋白下降至44g/L。入院后相关检查：血常规：白细胞3.76×10^9/L，中性粒细胞百分比64.3%，血红蛋白43 g/L，血小板223×10^9/L，红细胞1.42×10^9/L，MCV 83 fl，MCH 27.4 pg，MCHC 330 g/L，网织红细胞1.0%。粪便隐血阴性。KT/V：1.7。肝功能：总蛋白55.5 g/L，白蛋白43.6 g/L，总胆红素12.1umol/L，直接胆红素7umol/L，非结合胆红素5.1umol/L；电解质：钙2.3 mmo1/L，磷0.99 mmol/L，钾4.75 mmo1/L。血沉、CRP、PCT未见明显异常。铁蛋白 378.7 ng/ml；叶酸 20 ng/ml；维生素B12 1293 pg/ml；ANA、ENA、免疫球蛋白、ANCA、抗GBM、ASO、RA均阴性。Coomb’s试验、Ham试验均阴性。心电图：窦性心律。肺部CT：左上肺小结节，双肺陈旧性病灶。全腹CT：肝脏多发囊肿，副脾，左肾术后改变，右肾萎缩，盆腔少量积液。骨髓穿刺提示染色体正常，粒系增生欠活跃，红系、巨核系增生减低，血小板少见，骨髓部分血稀。你认为该血透患者贫血的病因是什么，列出依据。针对该患者贫血后续治疗，你有哪些方案？</t>
+        </is>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>该患者多次增加促红素剂量，血红蛋白不能维持靶目标值，甚至出现血红蛋白下降，根据目前的检查，排除了营养不良、溶血性贫血、血液系统疾病、恶性肿瘤、显性失血、自身免疫疾病等贫血性疾病，考虑该患者属于EPO低反应性贫血，即EPO抵抗。后续治疗方案：首先输血治疗，后续改善贫血方案可考虑：1停用促红素，改为罗沙司他治疗；11、雄激素联合促红素治疗。</t>
         </is>
       </c>
       <c r="N100" s="2"/>
